--- a/py/person.xlsx
+++ b/py/person.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27015" windowHeight="12765"/>
+    <workbookView windowWidth="26895" windowHeight="12765"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>name</t>
   </si>
@@ -41,9 +41,6 @@
   </si>
   <si>
     <t>崔斌斌</t>
-  </si>
-  <si>
-    <t>女</t>
   </si>
   <si>
     <t>C:\Users\DELL\Desktop\cbsQRCode.png</t>
@@ -1005,22 +1002,22 @@
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
+      <c r="B2">
+        <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
-      <c r="B3" t="s">
-        <v>4</v>
+      <c r="B3">
+        <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
